--- a/week-02/Saeteros_Ex3A_tables.xlsx
+++ b/week-02/Saeteros_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenni\Documents\DataAnalytics\week-02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7922064D-44D8-4CF9-A12A-4CB8F2F3DB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284E2641-B3EB-4AB5-9544-B4F716234D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="3195" windowWidth="17385" windowHeight="10208" activeTab="1" xr2:uid="{3C12D80C-5F41-461B-90F9-92D5962773CE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{3C12D80C-5F41-461B-90F9-92D5962773CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Customers" sheetId="1" r:id="rId1"/>
@@ -786,13 +786,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="10">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -803,13 +803,13 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="10">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -820,13 +820,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="10">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -837,13 +837,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="10">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -854,13 +854,13 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="10">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -871,13 +871,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="10">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -888,13 +888,13 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="10">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -905,13 +905,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="10">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -922,13 +922,13 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="10">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -939,13 +939,13 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="10">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -956,13 +956,13 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="10">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D12" s="3" t="s">
